--- a/experiments/results/densenet101/CIFAR-100/ReAct/adaptive/std/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-100/ReAct/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1154,6 +1154,398 @@
         <v>92.90000000000001</v>
       </c>
       <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>79.92</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>94.51000000000001</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>93.48</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>92.66</v>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.8,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>97.19</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>83.45999999999999</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>74.61</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>94.56999999999999</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>92.86</v>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.0,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>23.55</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>95.77</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>94.56</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>99.56</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>24.62</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>95.70999999999999</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>74.70999999999999</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>92.61</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>95.97</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>23.09</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>99.51000000000001</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>26.28</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>92.79000000000001</v>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=1.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>94.31</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>95.64</v>
+      </c>
+      <c r="M22" s="5" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="N22" s="5" t="n">
+        <v>92.92</v>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.4,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>97.70999999999999</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>95.48</v>
+      </c>
+      <c r="M23" s="5" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="N23" s="5" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.6,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>74.65000000000001</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>94.45999999999999</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>27.56</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=1.1,scale_th=0.5,type=std</t>
         </is>
